--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31.36507701695602</v>
+        <v>27.09288498401973</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>28.78665903935871</v>
+        <v>24.39080394412651</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>37.38138563134976</v>
+        <v>33.39774074377059</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.572942819194019</v>
+        <v>2.566635857819091</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>207931.5087602438</v>
+        <v>311398.3369400728</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.589257811211129</v>
+        <v>2.392283129542004</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6161.0485</v>
+        <v>5433.794050500462</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1784.2617</v>
+        <v>1605.679751173894</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1252.114</v>
+        <v>1179.332437399682</v>
       </c>
     </row>
     <row r="5">
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>6408.5692</v>
+        <v>5429.951239074038</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28.78665903935871</v>
+        <v>24.39080394412651</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30.19875912220329</v>
+        <v>25.70212715261699</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.412100082844582</v>
+        <v>-1.311323208490482</v>
       </c>
     </row>
   </sheetData>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>24.92869410206962</v>
+        <v>19.89070388759438</v>
       </c>
       <c r="F11" t="n">
-        <v>19.71164305329613</v>
+        <v>15.72799816571696</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>37.38138563134976</v>
+        <v>33.39774074377059</v>
       </c>
     </row>
     <row r="13">
@@ -1057,7 +1057,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22.20805915841229</v>
+        <v>18.79030553206326</v>
       </c>
       <c r="C2" t="n">
-        <v>25.98854990530301</v>
+        <v>22.14357707566035</v>
       </c>
       <c r="D2" t="n">
-        <v>29.76904065219374</v>
+        <v>25.49684861925745</v>
       </c>
       <c r="E2" t="n">
-        <v>33.54953139908446</v>
+        <v>28.85012016285454</v>
       </c>
       <c r="F2" t="n">
-        <v>37.33002214597519</v>
+        <v>32.20339170645164</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23.00607734079343</v>
+        <v>19.5883237144444</v>
       </c>
       <c r="C3" t="n">
-        <v>26.78656808768415</v>
+        <v>22.9415952580415</v>
       </c>
       <c r="D3" t="n">
-        <v>30.56705883457488</v>
+        <v>26.29486680163859</v>
       </c>
       <c r="E3" t="n">
-        <v>34.34754958146561</v>
+        <v>29.64813834523569</v>
       </c>
       <c r="F3" t="n">
-        <v>38.12804032835633</v>
+        <v>33.00140988883278</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.80409552317457</v>
+        <v>20.38634189682555</v>
       </c>
       <c r="C4" t="n">
-        <v>27.58458627006529</v>
+        <v>23.73961344042264</v>
       </c>
       <c r="D4" t="n">
-        <v>31.36507701695602</v>
+        <v>27.09288498401973</v>
       </c>
       <c r="E4" t="n">
-        <v>35.14556776384675</v>
+        <v>30.44615652761683</v>
       </c>
       <c r="F4" t="n">
-        <v>38.92605851073747</v>
+        <v>33.79942807121392</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.60211370555572</v>
+        <v>21.18436007920669</v>
       </c>
       <c r="C5" t="n">
-        <v>28.38260445244644</v>
+        <v>24.53763162280378</v>
       </c>
       <c r="D5" t="n">
-        <v>32.16309519933716</v>
+        <v>27.89090316640088</v>
       </c>
       <c r="E5" t="n">
-        <v>35.94358594622789</v>
+        <v>31.24417470999798</v>
       </c>
       <c r="F5" t="n">
-        <v>39.72407669311861</v>
+        <v>34.59744625359507</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25.40013188793686</v>
+        <v>21.98237826158783</v>
       </c>
       <c r="C6" t="n">
-        <v>29.18062263482759</v>
+        <v>25.33564980518493</v>
       </c>
       <c r="D6" t="n">
-        <v>32.96111338171831</v>
+        <v>28.68892134878202</v>
       </c>
       <c r="E6" t="n">
-        <v>36.74160412860903</v>
+        <v>32.04219289237912</v>
       </c>
       <c r="F6" t="n">
-        <v>40.52209487549976</v>
+        <v>35.39546443597621</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>30.53</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>31.37</v>
+        <v>27.09</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>31.64</v>
+        <v>27.37</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27.09288498401973</v>
+        <v>27.09491540762314</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24.39080394412651</v>
+        <v>24.39661354515648</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33.39774074377059</v>
+        <v>33.39095308671202</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.566635857819091</v>
+        <v>2.566579342876551</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>311398.3369400728</v>
+        <v>311331.659855852</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.392283129542004</v>
+        <v>2.391901479665804</v>
       </c>
     </row>
   </sheetData>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1605.679751173894</v>
+        <v>1606.973101339125</v>
       </c>
     </row>
     <row r="4">
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>5429.951239074038</v>
+        <v>5431.244589239267</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24.39080394412651</v>
+        <v>24.39661354515648</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25.70212715261699</v>
+        <v>25.70764845943717</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.311323208490482</v>
+        <v>-1.31103491428069</v>
       </c>
     </row>
   </sheetData>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>19.89070388759438</v>
+        <v>19.88211975150662</v>
       </c>
       <c r="F11" t="n">
-        <v>15.72799816571696</v>
+        <v>15.72121050865838</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>33.39774074377059</v>
+        <v>33.39095308671202</v>
       </c>
     </row>
     <row r="13">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.79030553206326</v>
+        <v>18.79192987094599</v>
       </c>
       <c r="C2" t="n">
-        <v>22.14357707566035</v>
+        <v>22.14540445690342</v>
       </c>
       <c r="D2" t="n">
-        <v>25.49684861925745</v>
+        <v>25.49887904286085</v>
       </c>
       <c r="E2" t="n">
-        <v>28.85012016285454</v>
+        <v>28.8523536288183</v>
       </c>
       <c r="F2" t="n">
-        <v>32.20339170645164</v>
+        <v>32.20582821477572</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.5883237144444</v>
+        <v>19.58994805332713</v>
       </c>
       <c r="C3" t="n">
-        <v>22.9415952580415</v>
+        <v>22.94342263928456</v>
       </c>
       <c r="D3" t="n">
-        <v>26.29486680163859</v>
+        <v>26.296897225242</v>
       </c>
       <c r="E3" t="n">
-        <v>29.64813834523569</v>
+        <v>29.65037181119944</v>
       </c>
       <c r="F3" t="n">
-        <v>33.00140988883278</v>
+        <v>33.00384639715686</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20.38634189682555</v>
+        <v>20.38796623570827</v>
       </c>
       <c r="C4" t="n">
-        <v>23.73961344042264</v>
+        <v>23.7414408216657</v>
       </c>
       <c r="D4" t="n">
-        <v>27.09288498401973</v>
+        <v>27.09491540762314</v>
       </c>
       <c r="E4" t="n">
-        <v>30.44615652761683</v>
+        <v>30.44838999358059</v>
       </c>
       <c r="F4" t="n">
-        <v>33.79942807121392</v>
+        <v>33.80186457953801</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.18436007920669</v>
+        <v>21.18598441808942</v>
       </c>
       <c r="C5" t="n">
-        <v>24.53763162280378</v>
+        <v>24.53945900404685</v>
       </c>
       <c r="D5" t="n">
-        <v>27.89090316640088</v>
+        <v>27.89293359000428</v>
       </c>
       <c r="E5" t="n">
-        <v>31.24417470999798</v>
+        <v>31.24640817596173</v>
       </c>
       <c r="F5" t="n">
-        <v>34.59744625359507</v>
+        <v>34.59988276191915</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.98237826158783</v>
+        <v>21.98400260047056</v>
       </c>
       <c r="C6" t="n">
-        <v>25.33564980518493</v>
+        <v>25.33747718642799</v>
       </c>
       <c r="D6" t="n">
-        <v>28.68892134878202</v>
+        <v>28.69095177238543</v>
       </c>
       <c r="E6" t="n">
-        <v>32.04219289237912</v>
+        <v>32.04442635834288</v>
       </c>
       <c r="F6" t="n">
-        <v>35.39546443597621</v>
+        <v>35.3979009443003</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>34.5</v>
+        <v>36.28</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>311331.659855852</v>
+        <v>354880.6886805243</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.391901479665804</v>
+        <v>2.726480322472769</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36.28</v>
+        <v>38.08</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>354880.6886805243</v>
+        <v>398919.0324358108</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.726480322472769</v>
+        <v>3.064818478120261</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.08</v>
+        <v>37.13</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>398919.0324358108</v>
+        <v>375676.5732316319</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.064818478120261</v>
+        <v>2.886251118195196</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37.13</v>
+        <v>40.93</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27.09491540762314</v>
+        <v>26.92539185225378</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24.39661354515648</v>
+        <v>24.0806303520509</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33.39095308671202</v>
+        <v>33.56316868606051</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>375676.5732316319</v>
+        <v>472015.1412802747</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.886251118195196</v>
+        <v>3.632385161819053</v>
       </c>
     </row>
   </sheetData>
@@ -612,7 +612,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5433.794050500462</v>
+        <v>5363.448959175854</v>
       </c>
     </row>
     <row r="3">
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>5431.244589239267</v>
+        <v>5360.899497914659</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24.39661354515648</v>
+        <v>24.0806303520509</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25.70764845943717</v>
+        <v>25.3752693858563</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.31103491428069</v>
+        <v>-1.294639033805396</v>
       </c>
     </row>
   </sheetData>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>19.88211975150662</v>
+        <v>20.0999153956422</v>
       </c>
       <c r="F11" t="n">
-        <v>15.72121050865838</v>
+        <v>15.89342610800688</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>33.39095308671202</v>
+        <v>33.56316868606051</v>
       </c>
     </row>
     <row r="13">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.79192987094599</v>
+        <v>18.6563110266505</v>
       </c>
       <c r="C2" t="n">
-        <v>22.14540445690342</v>
+        <v>21.992833257071</v>
       </c>
       <c r="D2" t="n">
-        <v>25.49887904286085</v>
+        <v>25.3293554874915</v>
       </c>
       <c r="E2" t="n">
-        <v>28.8523536288183</v>
+        <v>28.66587771791201</v>
       </c>
       <c r="F2" t="n">
-        <v>32.20582821477572</v>
+        <v>32.0023999483325</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.58994805332713</v>
+        <v>19.45432920903165</v>
       </c>
       <c r="C3" t="n">
-        <v>22.94342263928456</v>
+        <v>22.79085143945214</v>
       </c>
       <c r="D3" t="n">
-        <v>26.296897225242</v>
+        <v>26.12737366987264</v>
       </c>
       <c r="E3" t="n">
-        <v>29.65037181119944</v>
+        <v>29.46389590029316</v>
       </c>
       <c r="F3" t="n">
-        <v>33.00384639715686</v>
+        <v>32.80041813071365</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20.38796623570827</v>
+        <v>20.25234739141279</v>
       </c>
       <c r="C4" t="n">
-        <v>23.7414408216657</v>
+        <v>23.58886962183329</v>
       </c>
       <c r="D4" t="n">
-        <v>27.09491540762314</v>
+        <v>26.92539185225378</v>
       </c>
       <c r="E4" t="n">
-        <v>30.44838999358059</v>
+        <v>30.2619140826743</v>
       </c>
       <c r="F4" t="n">
-        <v>33.80186457953801</v>
+        <v>33.59843631309479</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.18598441808942</v>
+        <v>21.05036557379393</v>
       </c>
       <c r="C5" t="n">
-        <v>24.53945900404685</v>
+        <v>24.38688780421443</v>
       </c>
       <c r="D5" t="n">
-        <v>27.89293359000428</v>
+        <v>27.72341003463493</v>
       </c>
       <c r="E5" t="n">
-        <v>31.24640817596173</v>
+        <v>31.05993226505544</v>
       </c>
       <c r="F5" t="n">
-        <v>34.59988276191915</v>
+        <v>34.39645449547594</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.98400260047056</v>
+        <v>21.84838375617507</v>
       </c>
       <c r="C6" t="n">
-        <v>25.33747718642799</v>
+        <v>25.18490598659557</v>
       </c>
       <c r="D6" t="n">
-        <v>28.69095177238543</v>
+        <v>28.52142821701607</v>
       </c>
       <c r="E6" t="n">
-        <v>32.04442635834288</v>
+        <v>31.85795044743659</v>
       </c>
       <c r="F6" t="n">
-        <v>35.3979009443003</v>
+        <v>35.19447267785708</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>26.26</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>27.09</v>
+        <v>26.93</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>27.37</v>
+        <v>27.2</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.92539185225378</v>
+        <v>26.39775545080222</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33.56316868606051</v>
+        <v>31.80438068122197</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>472015.1412802747</v>
+        <v>469142.6826494932</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.632385161819053</v>
+        <v>3.610280201202559</v>
       </c>
     </row>
   </sheetData>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>20.0999153956422</v>
+        <v>17.87563160334423</v>
       </c>
       <c r="F11" t="n">
-        <v>15.89342610800688</v>
+        <v>14.13463810316834</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>33.56316868606051</v>
+        <v>31.80438068122197</v>
       </c>
     </row>
     <row r="13">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.6563110266505</v>
+        <v>18.20931132924752</v>
       </c>
       <c r="C2" t="n">
-        <v>21.992833257071</v>
+        <v>21.46843657498739</v>
       </c>
       <c r="D2" t="n">
-        <v>25.3293554874915</v>
+        <v>24.72756182072725</v>
       </c>
       <c r="E2" t="n">
-        <v>28.66587771791201</v>
+        <v>27.98668706646713</v>
       </c>
       <c r="F2" t="n">
-        <v>32.0023999483325</v>
+        <v>31.24581231220699</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.45432920903165</v>
+        <v>19.044408144285</v>
       </c>
       <c r="C3" t="n">
-        <v>22.79085143945214</v>
+        <v>22.30353339002487</v>
       </c>
       <c r="D3" t="n">
-        <v>26.12737366987264</v>
+        <v>25.56265863576473</v>
       </c>
       <c r="E3" t="n">
-        <v>29.46389590029316</v>
+        <v>28.82178388150462</v>
       </c>
       <c r="F3" t="n">
-        <v>32.80041813071365</v>
+        <v>32.08090912724448</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20.25234739141279</v>
+        <v>19.87950495932249</v>
       </c>
       <c r="C4" t="n">
-        <v>23.58886962183329</v>
+        <v>23.13863020506236</v>
       </c>
       <c r="D4" t="n">
-        <v>26.92539185225378</v>
+        <v>26.39775545080222</v>
       </c>
       <c r="E4" t="n">
-        <v>30.2619140826743</v>
+        <v>29.6568806965421</v>
       </c>
       <c r="F4" t="n">
-        <v>33.59843631309479</v>
+        <v>32.91600594228196</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.05036557379393</v>
+        <v>20.71460177435998</v>
       </c>
       <c r="C5" t="n">
-        <v>24.38688780421443</v>
+        <v>23.97372702009984</v>
       </c>
       <c r="D5" t="n">
-        <v>27.72341003463493</v>
+        <v>27.23285226583971</v>
       </c>
       <c r="E5" t="n">
-        <v>31.05993226505544</v>
+        <v>30.49197751157959</v>
       </c>
       <c r="F5" t="n">
-        <v>34.39645449547594</v>
+        <v>33.75110275731945</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.84838375617507</v>
+        <v>21.54969858939746</v>
       </c>
       <c r="C6" t="n">
-        <v>25.18490598659557</v>
+        <v>24.80882383513733</v>
       </c>
       <c r="D6" t="n">
-        <v>28.52142821701607</v>
+        <v>28.06794908087719</v>
       </c>
       <c r="E6" t="n">
-        <v>31.85795044743659</v>
+        <v>31.32707432661708</v>
       </c>
       <c r="F6" t="n">
-        <v>35.19447267785708</v>
+        <v>34.58619957235693</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>26.09</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>26.93</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>27.2</v>
+        <v>26.43</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.39775545080222</v>
+        <v>26.53518845194133</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24.0806303520509</v>
+        <v>24.21945126821137</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31.80438068122197</v>
+        <v>31.9385752139779</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.566579342876551</v>
+        <v>2.567406816641459</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>469142.6826494932</v>
+        <v>466274.2326850994</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.610280201202559</v>
+        <v>3.58559450033572</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5363.448959175854</v>
+        <v>5394.353672585123</v>
       </c>
     </row>
     <row r="3">
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>5360.899497914659</v>
+        <v>5391.804211323929</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24.0806303520509</v>
+        <v>24.21945126821137</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25.3752693858563</v>
+        <v>25.51539802310831</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.294639033805396</v>
+        <v>-1.295946754896942</v>
       </c>
     </row>
   </sheetData>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>17.87563160334423</v>
+        <v>18.04534320212865</v>
       </c>
       <c r="F11" t="n">
-        <v>14.13463810316834</v>
+        <v>14.26883263592426</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>31.80438068122197</v>
+        <v>31.9385752139779</v>
       </c>
     </row>
     <row r="13">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.20931132924752</v>
+        <v>18.3192577301588</v>
       </c>
       <c r="C2" t="n">
-        <v>21.46843657498739</v>
+        <v>21.59212627601257</v>
       </c>
       <c r="D2" t="n">
-        <v>24.72756182072725</v>
+        <v>24.86499482186635</v>
       </c>
       <c r="E2" t="n">
-        <v>27.98668706646713</v>
+        <v>28.13786336772014</v>
       </c>
       <c r="F2" t="n">
-        <v>31.24581231220699</v>
+        <v>31.41073191357392</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.044408144285</v>
+        <v>19.15435454519628</v>
       </c>
       <c r="C3" t="n">
-        <v>22.30353339002487</v>
+        <v>22.42722309105005</v>
       </c>
       <c r="D3" t="n">
-        <v>25.56265863576473</v>
+        <v>25.70009163690384</v>
       </c>
       <c r="E3" t="n">
-        <v>28.82178388150462</v>
+        <v>28.97296018275762</v>
       </c>
       <c r="F3" t="n">
-        <v>32.08090912724448</v>
+        <v>32.2458287286114</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.87950495932249</v>
+        <v>19.98945136023377</v>
       </c>
       <c r="C4" t="n">
-        <v>23.13863020506236</v>
+        <v>23.26231990608754</v>
       </c>
       <c r="D4" t="n">
-        <v>26.39775545080222</v>
+        <v>26.53518845194133</v>
       </c>
       <c r="E4" t="n">
-        <v>29.6568806965421</v>
+        <v>29.80805699779511</v>
       </c>
       <c r="F4" t="n">
-        <v>32.91600594228196</v>
+        <v>33.08092554364889</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.71460177435998</v>
+        <v>20.82454817527126</v>
       </c>
       <c r="C5" t="n">
-        <v>23.97372702009984</v>
+        <v>24.09741672112503</v>
       </c>
       <c r="D5" t="n">
-        <v>27.23285226583971</v>
+        <v>27.37028526697881</v>
       </c>
       <c r="E5" t="n">
-        <v>30.49197751157959</v>
+        <v>30.64315381283259</v>
       </c>
       <c r="F5" t="n">
-        <v>33.75110275731945</v>
+        <v>33.91602235868638</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.54969858939746</v>
+        <v>21.65964499030875</v>
       </c>
       <c r="C6" t="n">
-        <v>24.80882383513733</v>
+        <v>24.93251353616252</v>
       </c>
       <c r="D6" t="n">
-        <v>28.06794908087719</v>
+        <v>28.2053820820163</v>
       </c>
       <c r="E6" t="n">
-        <v>31.32707432661708</v>
+        <v>31.47825062787008</v>
       </c>
       <c r="F6" t="n">
-        <v>34.58619957235693</v>
+        <v>34.75111917372386</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>26.3</v>
+        <v>26.44</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>26.4</v>
+        <v>26.54</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>26.43</v>
+        <v>26.57</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40.93</v>
+        <v>35.52</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>466274.2326850994</v>
+        <v>339907.7376533884</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.58559450033572</v>
+        <v>2.613850882844408</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.53518845194133</v>
+        <v>25.28395474591364</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24.21945126821137</v>
+        <v>22.6668880523853</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31.9385752139779</v>
+        <v>31.39044369747976</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.567406816641459</v>
+        <v>2.557437978773745</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>339907.7376533884</v>
+        <v>366008.5563341072</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.613850882844408</v>
+        <v>2.838597346397533</v>
       </c>
     </row>
   </sheetData>
@@ -612,7 +612,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5394.353672585123</v>
+        <v>5048.717564122794</v>
       </c>
     </row>
     <row r="3">
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>5391.804211323929</v>
+        <v>5046.1681028616</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24.21945126821137</v>
+        <v>22.6668880523853</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25.51539802310831</v>
+        <v>23.90197283155594</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.295946754896942</v>
+        <v>-1.235084779170634</v>
       </c>
     </row>
   </sheetData>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>18.04534320212865</v>
+        <v>17.3521385379847</v>
       </c>
       <c r="F11" t="n">
-        <v>14.26883263592426</v>
+        <v>13.72070111942613</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>31.9385752139779</v>
+        <v>31.39044369747976</v>
       </c>
     </row>
     <row r="13">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.3192577301588</v>
+        <v>17.31827076533665</v>
       </c>
       <c r="C2" t="n">
-        <v>21.59212627601257</v>
+        <v>20.46601594058765</v>
       </c>
       <c r="D2" t="n">
-        <v>24.86499482186635</v>
+        <v>23.61376111583867</v>
       </c>
       <c r="E2" t="n">
-        <v>28.13786336772014</v>
+        <v>26.76150629108969</v>
       </c>
       <c r="F2" t="n">
-        <v>31.41073191357392</v>
+        <v>29.90925146634069</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.15435454519628</v>
+        <v>18.15336758037413</v>
       </c>
       <c r="C3" t="n">
-        <v>22.42722309105005</v>
+        <v>21.30111275562514</v>
       </c>
       <c r="D3" t="n">
-        <v>25.70009163690384</v>
+        <v>24.44885793087615</v>
       </c>
       <c r="E3" t="n">
-        <v>28.97296018275762</v>
+        <v>27.59660310612718</v>
       </c>
       <c r="F3" t="n">
-        <v>32.2458287286114</v>
+        <v>30.74434828137817</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.98945136023377</v>
+        <v>18.98846439541162</v>
       </c>
       <c r="C4" t="n">
-        <v>23.26231990608754</v>
+        <v>22.13620957066262</v>
       </c>
       <c r="D4" t="n">
-        <v>26.53518845194133</v>
+        <v>25.28395474591364</v>
       </c>
       <c r="E4" t="n">
-        <v>29.80805699779511</v>
+        <v>28.43169992116466</v>
       </c>
       <c r="F4" t="n">
-        <v>33.08092554364889</v>
+        <v>31.57944509641566</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.82454817527126</v>
+        <v>19.82356121044911</v>
       </c>
       <c r="C5" t="n">
-        <v>24.09741672112503</v>
+        <v>22.97130638570011</v>
       </c>
       <c r="D5" t="n">
-        <v>27.37028526697881</v>
+        <v>26.11905156095112</v>
       </c>
       <c r="E5" t="n">
-        <v>30.64315381283259</v>
+        <v>29.26679673620215</v>
       </c>
       <c r="F5" t="n">
-        <v>33.91602235868638</v>
+        <v>32.41454191145315</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.65964499030875</v>
+        <v>20.6586580254866</v>
       </c>
       <c r="C6" t="n">
-        <v>24.93251353616252</v>
+        <v>23.8064032007376</v>
       </c>
       <c r="D6" t="n">
-        <v>28.2053820820163</v>
+        <v>26.95414837598861</v>
       </c>
       <c r="E6" t="n">
-        <v>31.47825062787008</v>
+        <v>30.10189355123963</v>
       </c>
       <c r="F6" t="n">
-        <v>34.75111917372386</v>
+        <v>33.24963872649064</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>26.44</v>
+        <v>25.19</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>26.54</v>
+        <v>25.28</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>26.57</v>
+        <v>25.32</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35.52</v>
+        <v>35.44</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.28395474591364</v>
+        <v>26.53518845194133</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22.6668880523853</v>
+        <v>24.21945126821137</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31.39044369747976</v>
+        <v>31.9385752139779</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.557437978773745</v>
+        <v>2.567406816641459</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>366008.5563341072</v>
+        <v>338039.1018673371</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.838597346397533</v>
+        <v>2.599481291458214</v>
       </c>
     </row>
   </sheetData>
@@ -612,7 +612,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5048.717564122794</v>
+        <v>5394.353672585123</v>
       </c>
     </row>
     <row r="3">
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>5046.1681028616</v>
+        <v>5391.804211323929</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22.6668880523853</v>
+        <v>24.21945126821137</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>23.90197283155594</v>
+        <v>25.51539802310831</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.235084779170634</v>
+        <v>-1.295946754896942</v>
       </c>
     </row>
   </sheetData>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>17.3521385379847</v>
+        <v>18.04534320212865</v>
       </c>
       <c r="F11" t="n">
-        <v>13.72070111942613</v>
+        <v>14.26883263592426</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>31.39044369747976</v>
+        <v>31.9385752139779</v>
       </c>
     </row>
     <row r="13">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.31827076533665</v>
+        <v>18.3192577301588</v>
       </c>
       <c r="C2" t="n">
-        <v>20.46601594058765</v>
+        <v>21.59212627601257</v>
       </c>
       <c r="D2" t="n">
-        <v>23.61376111583867</v>
+        <v>24.86499482186635</v>
       </c>
       <c r="E2" t="n">
-        <v>26.76150629108969</v>
+        <v>28.13786336772014</v>
       </c>
       <c r="F2" t="n">
-        <v>29.90925146634069</v>
+        <v>31.41073191357392</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.15336758037413</v>
+        <v>19.15435454519628</v>
       </c>
       <c r="C3" t="n">
-        <v>21.30111275562514</v>
+        <v>22.42722309105005</v>
       </c>
       <c r="D3" t="n">
-        <v>24.44885793087615</v>
+        <v>25.70009163690384</v>
       </c>
       <c r="E3" t="n">
-        <v>27.59660310612718</v>
+        <v>28.97296018275762</v>
       </c>
       <c r="F3" t="n">
-        <v>30.74434828137817</v>
+        <v>32.2458287286114</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.98846439541162</v>
+        <v>19.98945136023377</v>
       </c>
       <c r="C4" t="n">
-        <v>22.13620957066262</v>
+        <v>23.26231990608754</v>
       </c>
       <c r="D4" t="n">
-        <v>25.28395474591364</v>
+        <v>26.53518845194133</v>
       </c>
       <c r="E4" t="n">
-        <v>28.43169992116466</v>
+        <v>29.80805699779511</v>
       </c>
       <c r="F4" t="n">
-        <v>31.57944509641566</v>
+        <v>33.08092554364889</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.82356121044911</v>
+        <v>20.82454817527126</v>
       </c>
       <c r="C5" t="n">
-        <v>22.97130638570011</v>
+        <v>24.09741672112503</v>
       </c>
       <c r="D5" t="n">
-        <v>26.11905156095112</v>
+        <v>27.37028526697881</v>
       </c>
       <c r="E5" t="n">
-        <v>29.26679673620215</v>
+        <v>30.64315381283259</v>
       </c>
       <c r="F5" t="n">
-        <v>32.41454191145315</v>
+        <v>33.91602235868638</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.6586580254866</v>
+        <v>21.65964499030875</v>
       </c>
       <c r="C6" t="n">
-        <v>23.8064032007376</v>
+        <v>24.93251353616252</v>
       </c>
       <c r="D6" t="n">
-        <v>26.95414837598861</v>
+        <v>28.2053820820163</v>
       </c>
       <c r="E6" t="n">
-        <v>30.10189355123963</v>
+        <v>31.47825062787008</v>
       </c>
       <c r="F6" t="n">
-        <v>33.24963872649064</v>
+        <v>34.75111917372386</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>25.19</v>
+        <v>26.44</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>25.28</v>
+        <v>26.54</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>25.32</v>
+        <v>26.57</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35.44</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>338039.1018673371</v>
+        <v>316082.6313812358</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.599481291458214</v>
+        <v>2.430638592670445</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>34.5</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>316082.6313812358</v>
+        <v>320754.2208463639</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.430638592670445</v>
+        <v>2.466562571135928</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>320754.2208463639</v>
+        <v>320754.2208463638</v>
       </c>
     </row>
     <row r="16">
@@ -1284,7 +1284,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>spot TCE VLCC: $388,300/day is 9.7x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
+          <t>spot TCE VLCC: $285,500/day is 7.1x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
         </is>
       </c>
     </row>

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>34.7</v>
+        <v>36.75</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>320754.2208463638</v>
+        <v>368638.0128639252</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.466562571135928</v>
+        <v>2.834783350407127</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36.75</v>
+        <v>36.56</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>368638.0128639252</v>
+        <v>364200.0028720536</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.834783350407127</v>
+        <v>2.800655570864918</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36.56</v>
+        <v>38.13</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>364200.0028720536</v>
+        <v>400871.9801733083</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.800655570864918</v>
+        <v>3.082658801818961</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.13</v>
+        <v>36.92</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>400871.9801733083</v>
+        <v>372608.8639092839</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.082658801818961</v>
+        <v>2.865318732102788</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36.92</v>
+        <v>38.38</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>372608.8639092839</v>
+        <v>406711.4670047181</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.865318732102788</v>
+        <v>3.127563774900814</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>406711.4670047181</v>
+        <v>406711.4670047182</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>406711.4670047182</v>
+        <v>406711.4670047181</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.38</v>
+        <v>36.49</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>406711.4670047182</v>
+        <v>362564.9465592591</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.127563774900814</v>
+        <v>2.788082178402001</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.53518845194133</v>
+        <v>26.41050122819077</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24.21945126821137</v>
+        <v>24.10733770901035</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31.9385752139779</v>
+        <v>31.78454943961176</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.567406816641459</v>
+        <v>2.566246593704207</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>362564.9465592591</v>
+        <v>365027.2897788474</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.788082178402001</v>
+        <v>2.810478484106679</v>
       </c>
     </row>
   </sheetData>
@@ -612,7 +612,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5394.353672585123</v>
+        <v>5357.939979328807</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1606.973101339125</v>
+        <v>1633.737959251722</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1179.332437399682</v>
+        <v>1164.022228297996</v>
       </c>
     </row>
     <row r="5">
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>5391.804211323929</v>
+        <v>5366.845166878525</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24.21945126821137</v>
+        <v>24.10733770901035</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25.51539802310831</v>
+        <v>25.40052807143319</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.295946754896942</v>
+        <v>-1.293190362422845</v>
       </c>
     </row>
   </sheetData>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>18.04534320212865</v>
+        <v>17.85055165671429</v>
       </c>
       <c r="F11" t="n">
-        <v>14.26883263592426</v>
+        <v>14.11480686155813</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>31.9385752139779</v>
+        <v>31.78454943961176</v>
       </c>
     </row>
     <row r="13">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.3192577301588</v>
+        <v>18.21950795115835</v>
       </c>
       <c r="C2" t="n">
-        <v>21.59212627601257</v>
+        <v>21.47990777463708</v>
       </c>
       <c r="D2" t="n">
-        <v>24.86499482186635</v>
+        <v>24.7403075981158</v>
       </c>
       <c r="E2" t="n">
-        <v>28.13786336772014</v>
+        <v>28.00070742159452</v>
       </c>
       <c r="F2" t="n">
-        <v>31.41073191357392</v>
+        <v>31.26110724507324</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.15435454519628</v>
+        <v>19.05460476619583</v>
       </c>
       <c r="C3" t="n">
-        <v>22.42722309105005</v>
+        <v>22.31500458967456</v>
       </c>
       <c r="D3" t="n">
-        <v>25.70009163690384</v>
+        <v>25.57540441315329</v>
       </c>
       <c r="E3" t="n">
-        <v>28.97296018275762</v>
+        <v>28.835804236632</v>
       </c>
       <c r="F3" t="n">
-        <v>32.2458287286114</v>
+        <v>32.09620406011073</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.98945136023377</v>
+        <v>19.88970158123332</v>
       </c>
       <c r="C4" t="n">
-        <v>23.26231990608754</v>
+        <v>23.15010140471205</v>
       </c>
       <c r="D4" t="n">
-        <v>26.53518845194133</v>
+        <v>26.41050122819077</v>
       </c>
       <c r="E4" t="n">
-        <v>29.80805699779511</v>
+        <v>29.67090105166949</v>
       </c>
       <c r="F4" t="n">
-        <v>33.08092554364889</v>
+        <v>32.93130087514822</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.82454817527126</v>
+        <v>20.72479839627081</v>
       </c>
       <c r="C5" t="n">
-        <v>24.09741672112503</v>
+        <v>23.98519821974953</v>
       </c>
       <c r="D5" t="n">
-        <v>27.37028526697881</v>
+        <v>27.24559804322826</v>
       </c>
       <c r="E5" t="n">
-        <v>30.64315381283259</v>
+        <v>30.50599786670698</v>
       </c>
       <c r="F5" t="n">
-        <v>33.91602235868638</v>
+        <v>33.7663976901857</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.65964499030875</v>
+        <v>21.55989521130829</v>
       </c>
       <c r="C6" t="n">
-        <v>24.93251353616252</v>
+        <v>24.82029503478702</v>
       </c>
       <c r="D6" t="n">
-        <v>28.2053820820163</v>
+        <v>28.08069485826574</v>
       </c>
       <c r="E6" t="n">
-        <v>31.47825062787008</v>
+        <v>31.34109468174447</v>
       </c>
       <c r="F6" t="n">
-        <v>34.75111917372386</v>
+        <v>34.60149450522319</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>26.44</v>
+        <v>26.31</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>26.54</v>
+        <v>26.41</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>26.57</v>
+        <v>26.44</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36.49</v>
+        <v>36.93</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>365027.2897788474</v>
+        <v>375292.129612088</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.810478484106679</v>
+        <v>2.889511236730741</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36.93</v>
+        <v>39.29</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>375292.129612088</v>
+        <v>430348.9978085594</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.889511236730741</v>
+        <v>3.313414182623438</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39.29</v>
+        <v>39.34</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>430348.9978085594</v>
+        <v>431515.4568805187</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.313414182623438</v>
+        <v>3.32239517723981</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39.34</v>
+        <v>39.74</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>431515.4568805187</v>
+        <v>440847.1294561919</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.32239517723981</v>
+        <v>3.394243134170776</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.41050122819077</v>
+        <v>27.60060973075172</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24.10733770901035</v>
+        <v>25.3370224545083</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31.78454943961176</v>
+        <v>32.88231337531971</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.566246593704207</v>
+        <v>2.574792941616729</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>440847.1294561919</v>
+        <v>416149.9763217981</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.394243134170776</v>
+        <v>3.180475973082838</v>
       </c>
     </row>
   </sheetData>
@@ -612,7 +612,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5357.939979328807</v>
+        <v>5647.804712946339</v>
       </c>
     </row>
     <row r="3">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1164.022228297996</v>
+        <v>1147.913465282448</v>
       </c>
     </row>
     <row r="5">
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>5366.845166878525</v>
+        <v>5640.601137480508</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24.10733770901035</v>
+        <v>25.3370224545083</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25.40052807143319</v>
+        <v>26.63373735518205</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.293190362422845</v>
+        <v>-1.296714900673745</v>
       </c>
     </row>
   </sheetData>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>17.85055165671429</v>
+        <v>19.23885912938697</v>
       </c>
       <c r="F11" t="n">
-        <v>14.11480686155813</v>
+        <v>15.21257079726607</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>31.78454943961176</v>
+        <v>32.88231337531971</v>
       </c>
     </row>
     <row r="13">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.21950795115835</v>
+        <v>19.17159475320711</v>
       </c>
       <c r="C2" t="n">
-        <v>21.47990777463708</v>
+        <v>22.55100542694193</v>
       </c>
       <c r="D2" t="n">
-        <v>24.7403075981158</v>
+        <v>25.93041610067675</v>
       </c>
       <c r="E2" t="n">
-        <v>28.00070742159452</v>
+        <v>29.30982677441157</v>
       </c>
       <c r="F2" t="n">
-        <v>31.26110724507324</v>
+        <v>32.68923744814638</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.05460476619583</v>
+        <v>20.00669156824459</v>
       </c>
       <c r="C3" t="n">
-        <v>22.31500458967456</v>
+        <v>23.38610224197941</v>
       </c>
       <c r="D3" t="n">
-        <v>25.57540441315329</v>
+        <v>26.76551291571423</v>
       </c>
       <c r="E3" t="n">
-        <v>28.835804236632</v>
+        <v>30.14492358944905</v>
       </c>
       <c r="F3" t="n">
-        <v>32.09620406011073</v>
+        <v>33.52433426318387</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.88970158123332</v>
+        <v>20.84178838328208</v>
       </c>
       <c r="C4" t="n">
-        <v>23.15010140471205</v>
+        <v>24.2211990570169</v>
       </c>
       <c r="D4" t="n">
-        <v>26.41050122819077</v>
+        <v>27.60060973075172</v>
       </c>
       <c r="E4" t="n">
-        <v>29.67090105166949</v>
+        <v>30.98002040448654</v>
       </c>
       <c r="F4" t="n">
-        <v>32.93130087514822</v>
+        <v>34.35943107822136</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.72479839627081</v>
+        <v>21.67688519831957</v>
       </c>
       <c r="C5" t="n">
-        <v>23.98519821974953</v>
+        <v>25.05629587205438</v>
       </c>
       <c r="D5" t="n">
-        <v>27.24559804322826</v>
+        <v>28.43570654578921</v>
       </c>
       <c r="E5" t="n">
-        <v>30.50599786670698</v>
+        <v>31.81511721952403</v>
       </c>
       <c r="F5" t="n">
-        <v>33.7663976901857</v>
+        <v>35.19452789325884</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.55989521130829</v>
+        <v>22.51198201335706</v>
       </c>
       <c r="C6" t="n">
-        <v>24.82029503478702</v>
+        <v>25.89139268709187</v>
       </c>
       <c r="D6" t="n">
-        <v>28.08069485826574</v>
+        <v>29.27080336082669</v>
       </c>
       <c r="E6" t="n">
-        <v>31.34109468174447</v>
+        <v>32.65021403456151</v>
       </c>
       <c r="F6" t="n">
-        <v>34.60149450522319</v>
+        <v>36.02962470829632</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>26.31</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>26.41</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>26.44</v>
+        <v>27.63</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27.60060973075172</v>
+        <v>25.93915440837203</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32.88231337531971</v>
+        <v>27.34412896738741</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>111500</v>
+        <v>105700</v>
       </c>
     </row>
     <row r="10">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>155000</v>
+        <v>142675</v>
       </c>
     </row>
     <row r="11">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.574792941616729</v>
+        <v>2.431591448970646</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>416149.9763217981</v>
+        <v>545467.9350004614</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.180475973082838</v>
+        <v>4.533372157888817</v>
       </c>
     </row>
   </sheetData>
@@ -827,19 +827,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>147500</v>
+        <v>179650</v>
       </c>
       <c r="C2" t="n">
-        <v>128750</v>
+        <v>151255</v>
       </c>
       <c r="D2" t="n">
-        <v>2.592009958986068</v>
+        <v>3.093662310030933</v>
       </c>
       <c r="E2" t="n">
-        <v>2.462409461036765</v>
+        <v>2.938979194529386</v>
       </c>
       <c r="F2" t="n">
-        <v>2.398996014323648</v>
+        <v>2.863292837937505</v>
       </c>
     </row>
     <row r="3">
@@ -849,19 +849,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>183500</v>
+        <v>179650</v>
       </c>
       <c r="C3" t="n">
-        <v>153950</v>
+        <v>151255</v>
       </c>
       <c r="D3" t="n">
-        <v>3.296654021107865</v>
+        <v>3.207275463902321</v>
       </c>
       <c r="E3" t="n">
-        <v>3.131821320052472</v>
+        <v>3.046911690707205</v>
       </c>
       <c r="F3" t="n">
-        <v>2.97259324719595</v>
+        <v>2.892000593586509</v>
       </c>
     </row>
     <row r="4">
@@ -871,19 +871,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>165500</v>
+        <v>105700</v>
       </c>
       <c r="C4" t="n">
-        <v>141350</v>
+        <v>99490</v>
       </c>
       <c r="D4" t="n">
-        <v>3.086614284737249</v>
+        <v>1.957937626759484</v>
       </c>
       <c r="E4" t="n">
-        <v>2.932283570500387</v>
+        <v>1.860040745421509</v>
       </c>
       <c r="F4" t="n">
-        <v>2.711525749282142</v>
+        <v>1.720007037062825</v>
       </c>
     </row>
     <row r="5">
@@ -893,19 +893,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>123500</v>
+        <v>105700</v>
       </c>
       <c r="C5" t="n">
-        <v>111950</v>
+        <v>99490</v>
       </c>
       <c r="D5" t="n">
-        <v>2.332387377163406</v>
+        <v>1.97595461564096</v>
       </c>
       <c r="E5" t="n">
-        <v>2.215768008305235</v>
+        <v>1.877156884858912</v>
       </c>
       <c r="F5" t="n">
-        <v>1.996187394869581</v>
+        <v>1.691132328701722</v>
       </c>
     </row>
     <row r="6">
@@ -915,19 +915,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>111500</v>
+        <v>48850</v>
       </c>
       <c r="C6" t="n">
-        <v>103550</v>
+        <v>59695</v>
       </c>
       <c r="D6" t="n">
-        <v>2.106844261833742</v>
+        <v>1.004403719646837</v>
       </c>
       <c r="E6" t="n">
-        <v>2.001502048742054</v>
+        <v>0.9541835336644955</v>
       </c>
       <c r="F6" t="n">
-        <v>1.756719068837441</v>
+        <v>0.8374872310586068</v>
       </c>
     </row>
     <row r="7">
@@ -937,19 +937,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>135500</v>
+        <v>48850</v>
       </c>
       <c r="C7" t="n">
-        <v>120350</v>
+        <v>59695</v>
       </c>
       <c r="D7" t="n">
-        <v>2.585017335807281</v>
+        <v>1.004403719646837</v>
       </c>
       <c r="E7" t="n">
-        <v>2.455766469016917</v>
+        <v>0.9541835336644955</v>
       </c>
       <c r="F7" t="n">
-        <v>2.099919261052511</v>
+        <v>0.8159197571108374</v>
       </c>
     </row>
     <row r="8">
@@ -959,19 +959,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>147500</v>
+        <v>48850</v>
       </c>
       <c r="C8" t="n">
-        <v>128750</v>
+        <v>59695</v>
       </c>
       <c r="D8" t="n">
-        <v>2.776611607516467</v>
+        <v>1.004403719646837</v>
       </c>
       <c r="E8" t="n">
-        <v>2.637781027140643</v>
+        <v>0.9541835336644955</v>
       </c>
       <c r="F8" t="n">
-        <v>2.197472896874812</v>
+        <v>0.7949077016998972</v>
       </c>
     </row>
     <row r="9">
@@ -981,19 +981,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>105500</v>
+        <v>48850</v>
       </c>
       <c r="C9" t="n">
-        <v>99350</v>
+        <v>59695</v>
       </c>
       <c r="D9" t="n">
-        <v>1.992537783047771</v>
+        <v>1.004403719646837</v>
       </c>
       <c r="E9" t="n">
-        <v>1.892910893895382</v>
+        <v>0.9541835336644955</v>
       </c>
       <c r="F9" t="n">
-        <v>1.536328945617549</v>
+        <v>0.7744367613541883</v>
       </c>
     </row>
     <row r="10">
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>17.66974257805363</v>
+        <v>12.38918424851209</v>
       </c>
     </row>
     <row r="11">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>19.23885912938697</v>
+        <v>18.91304754262303</v>
       </c>
       <c r="F11" t="n">
-        <v>15.21257079726607</v>
+        <v>14.95494471887532</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>32.88231337531971</v>
+        <v>27.34412896738741</v>
       </c>
     </row>
     <row r="13">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>155000</v>
+        <v>142675</v>
       </c>
     </row>
   </sheetData>
@@ -1058,7 +1058,7 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.17159475320711</v>
+        <v>18.00857602754133</v>
       </c>
       <c r="C2" t="n">
-        <v>22.55100542694193</v>
+        <v>21.38798670127614</v>
       </c>
       <c r="D2" t="n">
-        <v>25.93041610067675</v>
+        <v>24.76739737501097</v>
       </c>
       <c r="E2" t="n">
-        <v>29.30982677441157</v>
+        <v>28.14680804874579</v>
       </c>
       <c r="F2" t="n">
-        <v>32.68923744814638</v>
+        <v>31.5262187224806</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.00669156824459</v>
+        <v>18.59445454422186</v>
       </c>
       <c r="C3" t="n">
-        <v>23.38610224197941</v>
+        <v>21.97386521795668</v>
       </c>
       <c r="D3" t="n">
-        <v>26.76551291571423</v>
+        <v>25.3532758916915</v>
       </c>
       <c r="E3" t="n">
-        <v>30.14492358944905</v>
+        <v>28.73268656542632</v>
       </c>
       <c r="F3" t="n">
-        <v>33.52433426318387</v>
+        <v>32.11209723916113</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20.84178838328208</v>
+        <v>19.18033306090239</v>
       </c>
       <c r="C4" t="n">
-        <v>24.2211990570169</v>
+        <v>22.55974373463721</v>
       </c>
       <c r="D4" t="n">
-        <v>27.60060973075172</v>
+        <v>25.93915440837203</v>
       </c>
       <c r="E4" t="n">
-        <v>30.98002040448654</v>
+        <v>29.31856508210685</v>
       </c>
       <c r="F4" t="n">
-        <v>34.35943107822136</v>
+        <v>32.69797575584167</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.67688519831957</v>
+        <v>19.76621157758293</v>
       </c>
       <c r="C5" t="n">
-        <v>25.05629587205438</v>
+        <v>23.14562225131775</v>
       </c>
       <c r="D5" t="n">
-        <v>28.43570654578921</v>
+        <v>26.52503292505256</v>
       </c>
       <c r="E5" t="n">
-        <v>31.81511721952403</v>
+        <v>29.90444359878739</v>
       </c>
       <c r="F5" t="n">
-        <v>35.19452789325884</v>
+        <v>33.2838542725222</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22.51198201335706</v>
+        <v>20.35209009426346</v>
       </c>
       <c r="C6" t="n">
-        <v>25.89139268709187</v>
+        <v>23.73150076799828</v>
       </c>
       <c r="D6" t="n">
-        <v>29.27080336082669</v>
+        <v>27.1109114417331</v>
       </c>
       <c r="E6" t="n">
-        <v>32.65021403456151</v>
+        <v>30.49032211546792</v>
       </c>
       <c r="F6" t="n">
-        <v>36.02962470829632</v>
+        <v>33.86973278920273</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>27.5</v>
+        <v>25.86</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>27.6</v>
+        <v>25.94</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>27.63</v>
+        <v>25.97</v>
       </c>
     </row>
   </sheetData>
@@ -1284,7 +1284,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>spot TCE VLCC: $285,500/day is 7.1x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
+          <t>spot TCE VLCC: $488,900/day is 12.2x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
         </is>
       </c>
     </row>

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39.74</v>
+        <v>39.57</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>545467.9350004614</v>
+        <v>540230.9604913163</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.533372157888817</v>
+        <v>4.48984777651283</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39.57</v>
+        <v>41.21</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>540230.9604913163</v>
+        <v>590752.3616383619</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.48984777651283</v>
+        <v>4.909730043904689</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41.21</v>
+        <v>43.46</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>590752.3616383619</v>
+        <v>660065.2595535155</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.909730043904689</v>
+        <v>5.485788032704491</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43.46</v>
+        <v>44.19</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>660065.2595535155</v>
+        <v>682553.4442104318</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.485788032704491</v>
+        <v>5.672686846848425</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fro_fv_report.xlsx
+++ b/outputs/fro_fv_report.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
     </row>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.93915440837203</v>
+        <v>26.58282151672109</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25.3370224545083</v>
+        <v>26.04361839785108</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.34412896738741</v>
+        <v>27.8409621274178</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.431591448970646</v>
+        <v>2.436382838993574</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>682553.4442104318</v>
+        <v>715732.6673444344</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.672686846848425</v>
+        <v>5.923067095875524</v>
       </c>
     </row>
   </sheetData>
@@ -612,7 +612,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5647.804712946339</v>
+        <v>5542.027762882259</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1633.737959251722</v>
+        <v>1478.692453834185</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1147.913465282448</v>
+        <v>1122.797351026714</v>
       </c>
     </row>
     <row r="5">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>471.672</v>
+        <v>322.307</v>
       </c>
     </row>
     <row r="6">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>295.56</v>
+        <v>368.023</v>
       </c>
     </row>
     <row r="7">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-2631.087</v>
+        <v>-2434.842</v>
       </c>
     </row>
     <row r="8">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-925</v>
+        <v>-601.1</v>
       </c>
     </row>
     <row r="10">
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>5640.601137480508</v>
+        <v>5797.905567743158</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25.3370224545083</v>
+        <v>26.04361839785108</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26.63373735518205</v>
+        <v>27.25215875039183</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.296714900673745</v>
+        <v>-1.208540352540751</v>
       </c>
     </row>
   </sheetData>
@@ -830,16 +830,16 @@
         <v>179650</v>
       </c>
       <c r="C2" t="n">
-        <v>151255</v>
+        <v>144808.8235294118</v>
       </c>
       <c r="D2" t="n">
-        <v>3.093662310030933</v>
+        <v>2.965015192881608</v>
       </c>
       <c r="E2" t="n">
-        <v>2.938979194529386</v>
+        <v>2.816764433237527</v>
       </c>
       <c r="F2" t="n">
-        <v>2.863292837937505</v>
+        <v>2.744225424548328</v>
       </c>
     </row>
     <row r="3">
@@ -852,16 +852,16 @@
         <v>179650</v>
       </c>
       <c r="C3" t="n">
-        <v>151255</v>
+        <v>144808.8235294118</v>
       </c>
       <c r="D3" t="n">
-        <v>3.207275463902321</v>
+        <v>3.100564725145488</v>
       </c>
       <c r="E3" t="n">
-        <v>3.046911690707205</v>
+        <v>2.945536488888214</v>
       </c>
       <c r="F3" t="n">
-        <v>2.892000593586509</v>
+        <v>2.79577951020899</v>
       </c>
     </row>
     <row r="4">
@@ -874,16 +874,16 @@
         <v>105700</v>
       </c>
       <c r="C4" t="n">
-        <v>99490</v>
+        <v>100438.8235294118</v>
       </c>
       <c r="D4" t="n">
-        <v>1.957937626759484</v>
+        <v>1.917347593777425</v>
       </c>
       <c r="E4" t="n">
-        <v>1.860040745421509</v>
+        <v>1.821480214088554</v>
       </c>
       <c r="F4" t="n">
-        <v>1.720007037062825</v>
+        <v>1.684349546543425</v>
       </c>
     </row>
     <row r="5">
@@ -896,16 +896,16 @@
         <v>105700</v>
       </c>
       <c r="C5" t="n">
-        <v>99490</v>
+        <v>100438.8235294118</v>
       </c>
       <c r="D5" t="n">
-        <v>1.97595461564096</v>
+        <v>1.917347593777425</v>
       </c>
       <c r="E5" t="n">
-        <v>1.877156884858912</v>
+        <v>1.821480214088554</v>
       </c>
       <c r="F5" t="n">
-        <v>1.691132328701722</v>
+        <v>1.640973165845544</v>
       </c>
     </row>
     <row r="6">
@@ -918,16 +918,16 @@
         <v>48850</v>
       </c>
       <c r="C6" t="n">
-        <v>59695</v>
+        <v>66328.82352941178</v>
       </c>
       <c r="D6" t="n">
-        <v>1.004403719646837</v>
+        <v>1.05324559041525</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9541835336644955</v>
+        <v>1.000583310894488</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8374872310586068</v>
+        <v>0.8782123322399755</v>
       </c>
     </row>
     <row r="7">
@@ -940,16 +940,16 @@
         <v>48850</v>
       </c>
       <c r="C7" t="n">
-        <v>59695</v>
+        <v>66328.82352941178</v>
       </c>
       <c r="D7" t="n">
-        <v>1.004403719646837</v>
+        <v>1.05324559041525</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9541835336644955</v>
+        <v>1.000583310894488</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8159197571108374</v>
+        <v>0.8555960810378482</v>
       </c>
     </row>
     <row r="8">
@@ -962,16 +962,16 @@
         <v>48850</v>
       </c>
       <c r="C8" t="n">
-        <v>59695</v>
+        <v>66328.82352941178</v>
       </c>
       <c r="D8" t="n">
-        <v>1.004403719646837</v>
+        <v>1.05324559041525</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9541835336644955</v>
+        <v>1.000583310894488</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7949077016998972</v>
+        <v>0.833562257114023</v>
       </c>
     </row>
     <row r="9">
@@ -984,16 +984,16 @@
         <v>48850</v>
       </c>
       <c r="C9" t="n">
-        <v>59695</v>
+        <v>66328.82352941178</v>
       </c>
       <c r="D9" t="n">
-        <v>1.004403719646837</v>
+        <v>1.05324559041525</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9541835336644955</v>
+        <v>1.000583310894488</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7744367613541883</v>
+        <v>0.8120958614515768</v>
       </c>
     </row>
     <row r="10">
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>12.38918424851209</v>
+        <v>12.24479417898971</v>
       </c>
     </row>
     <row r="11">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>18.91304754262303</v>
+        <v>19.72398236411114</v>
       </c>
       <c r="F11" t="n">
-        <v>14.95494471887532</v>
+        <v>15.59616794842809</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>27.34412896738741</v>
+        <v>27.8409621274178</v>
       </c>
     </row>
     <row r="13">
@@ -1058,7 +1058,7 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.00857602754133</v>
+        <v>18.98653382075678</v>
       </c>
       <c r="C2" t="n">
-        <v>21.38798670127614</v>
+        <v>22.24820787845221</v>
       </c>
       <c r="D2" t="n">
-        <v>24.76739737501097</v>
+        <v>25.50988193614763</v>
       </c>
       <c r="E2" t="n">
-        <v>28.14680804874579</v>
+        <v>28.77155599384307</v>
       </c>
       <c r="F2" t="n">
-        <v>31.5262187224806</v>
+        <v>32.03323005153849</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.59445454422186</v>
+        <v>19.52300361104351</v>
       </c>
       <c r="C3" t="n">
-        <v>21.97386521795668</v>
+        <v>22.78467766873894</v>
       </c>
       <c r="D3" t="n">
-        <v>25.3532758916915</v>
+        <v>26.04635172643436</v>
       </c>
       <c r="E3" t="n">
-        <v>28.73268656542632</v>
+        <v>29.3080257841298</v>
       </c>
       <c r="F3" t="n">
-        <v>32.11209723916113</v>
+        <v>32.56969984182522</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.18033306090239</v>
+        <v>20.05947340133024</v>
       </c>
       <c r="C4" t="n">
-        <v>22.55974373463721</v>
+        <v>23.32114745902567</v>
       </c>
       <c r="D4" t="n">
-        <v>25.93915440837203</v>
+        <v>26.58282151672109</v>
       </c>
       <c r="E4" t="n">
-        <v>29.31856508210685</v>
+        <v>29.84449557441653</v>
       </c>
       <c r="F4" t="n">
-        <v>32.69797575584167</v>
+        <v>33.10616963211195</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.76621157758293</v>
+        <v>20.59594319161697</v>
       </c>
       <c r="C5" t="n">
-        <v>23.14562225131775</v>
+        <v>23.8576172493124</v>
       </c>
       <c r="D5" t="n">
-        <v>26.52503292505256</v>
+        <v>27.11929130700782</v>
       </c>
       <c r="E5" t="n">
-        <v>29.90444359878739</v>
+        <v>30.38096536470325</v>
       </c>
       <c r="F5" t="n">
-        <v>33.2838542725222</v>
+        <v>33.64263942239867</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.35209009426346</v>
+        <v>21.13241298190369</v>
       </c>
       <c r="C6" t="n">
-        <v>23.73150076799828</v>
+        <v>24.39408703959912</v>
       </c>
       <c r="D6" t="n">
-        <v>27.1109114417331</v>
+        <v>27.65576109729454</v>
       </c>
       <c r="E6" t="n">
-        <v>30.49032211546792</v>
+        <v>30.91743515498998</v>
       </c>
       <c r="F6" t="n">
-        <v>33.86973278920273</v>
+        <v>34.1791092126854</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>25.86</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>25.94</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>25.97</v>
+        <v>26.61</v>
       </c>
     </row>
   </sheetData>
